--- a/archivos/Acreditaciones.xlsx
+++ b/archivos/Acreditaciones.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t xml:space="preserve">Nº</t>
   </si>
@@ -43,145 +43,206 @@
     <t xml:space="preserve"> Acreditar</t>
   </si>
   <si>
+    <t xml:space="preserve">ALMIRON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA DEL ROSARIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S.C.de BARILOCHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALERIA JORGELINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIPOLLETTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUTVILOFSKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LAURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIEL GISELLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAL. ROCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMAMALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRERAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIERRA GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAL BIANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA ALEXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESCALANTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVANA PAOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLSÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARRIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERNA DEL CARMEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVANA GABRIELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JIMENEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIA AGOSTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIEDMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA PAULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARILOCHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLA SOLEDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERAL ROCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELA YOLANDA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S.C.de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> BARILOCHE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PALOMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALTER DAMIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ING. HUERGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUIROZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELINA AYLEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIOSECO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELEN ANABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAVIERA MABEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROMAN</t>
   </si>
   <si>
     <t xml:space="preserve">VILMA LAUREANA</t>
   </si>
   <si>
-    <t xml:space="preserve">SIERRA GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALMIRON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA DEL ROSARIO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">S.C.de BARILOCHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAVON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TATIANA MABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIPOLLETTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBAÑEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REBECA ELIZABETH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIEDMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DI FIORE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANCY PATRICIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SILVANA GABRIELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIOSECO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BELEN ANABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUIROZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MELINA AYLEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GISELLA MARIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENERAL ROCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALOMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WALTER DAMIAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ING. HUERGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTRERAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMAMALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VANINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCELA YOLANDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARRIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERNA DEL CARMEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIQUEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAREN HERMINDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAL BIANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA ALEXA</t>
+    <t xml:space="preserve">TARABORELLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROLINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÁNGELES VICTORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOLOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORENCIA SOLEDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEATRIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VASQUEZ PEZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALERIA GINETTE</t>
   </si>
   <si>
     <t xml:space="preserve">VIDAL</t>
   </si>
   <si>
     <t xml:space="preserve">VIDALITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERVANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARLA SOLEDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUIRRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUGENIA HEBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL BOLSON</t>
   </si>
 </sst>
 </file>
@@ -193,9 +254,9 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="[$$-2C0A]#,##0.00;[RED]\([$$-2C0A]#,##0.00\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -217,7 +278,51 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000009"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -225,47 +330,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <u val="single"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF0C1E2B"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000009"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="TimES NEW ROMAN"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -275,12 +350,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9F9F9"/>
-        <bgColor rgb="FFF6F8F9"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -294,8 +363,14 @@
         <bgColor rgb="FFF9F9F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F9F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -308,6 +383,13 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -336,52 +418,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -389,19 +467,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -494,40 +572,40 @@
         <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
         <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -535,25 +613,67 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -572,11 +692,35 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -588,10 +732,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.08"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -615,151 +762,151 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>22418974</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>27224189740</v>
+      <c r="F2" s="6" t="n">
+        <v>10152013</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>27101520132</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>10152013</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>27101520132</v>
+      <c r="F3" s="6" t="n">
+        <v>29919514</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>27299195142</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>28667931</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>27286679310</v>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>26307040</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>27263070408</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>33823859</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>27338238598</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>606900</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="6" t="n">
+        <v>34667675</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>27346676758</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1213800</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>30479727</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>23304797274</v>
+      <c r="E6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>24318207</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>27243182072</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>22497523</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>27224975231</v>
+      <c r="F7" s="6" t="n">
+        <v>22701911</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>27227019110</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
       <c r="B8" s="6" t="n">
         <v>7</v>
@@ -767,185 +914,185 @@
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>34952093</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>27349520937</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>1213800</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>23831193</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>23238311934</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1820700</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
       <c r="B9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>43435039</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>27434350390</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>606900</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="7" t="n">
+        <v>24054807</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>27240548076</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1213800</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>34667675</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>27346676758</v>
+      <c r="E10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>93902592</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>27939025923</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>1213800</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="6" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>33919346</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>20339193461</v>
+        <v>9</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>22497523</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>27224975231</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
       <c r="B12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>22701911</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>27227019110</v>
+      <c r="F12" s="6" t="n">
+        <v>36850297</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>27368502974</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>24318207</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>27243182072</v>
+      <c r="F13" s="6" t="n">
+        <v>27340288</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>27273402883</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>18493541</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>23184935414</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>606900</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>35598371</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>23355983714</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>93902592</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>27939025923</v>
+      <c r="D15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>18493541</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>23184935414</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>606900</v>
@@ -956,118 +1103,262 @@
       <c r="B16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>39354627</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>27393546277</v>
+      <c r="C16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>33919346</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>20339193461</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>23831193</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>23238311934</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>1820700</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>43435039</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>27434350390</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>18067059</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>27180670594</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>606900</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>34952093</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>27349520937</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1213800</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>35598371</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>23355983714</v>
+      <c r="C19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>27489297</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>27274892973</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>39267543</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>23392675434</v>
+      <c r="C20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>22418974</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>27224189740</v>
       </c>
       <c r="H20" s="7" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>33772073</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>27337720730</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>37603253</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>27376032537</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>38091874</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>27380918744</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1"/>
+      <c r="B24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>22139086</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>27221390860</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>606900</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1"/>
+      <c r="B25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>92651717</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>27926517177</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1213800</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1"/>
+      <c r="B26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>18067059</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>27180670594</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <v>606900</v>
       </c>
     </row>
